--- a/04_Figures/F06_prediction/modules/trajectory/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/trajectory/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -222,24 +222,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise@T1</t>
@@ -644,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -677,7 +659,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -689,16 +671,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.213930348258706</v>
+        <v>0.218905472636816</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.160428554144742</v>
+        <v>-0.160282462828254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0142409463220459</v>
+        <v>0.0151715517101875</v>
       </c>
     </row>
     <row r="4">
@@ -718,7 +700,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -751,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -763,16 +745,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.840796019900497</v>
+        <v>0.870646766169154</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.161887593928464</v>
+        <v>-0.161150843414758</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0140472303146036</v>
+        <v>0.0143155846319513</v>
       </c>
     </row>
     <row r="6">
@@ -792,7 +774,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -825,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -837,16 +819,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.427860696517413</v>
+        <v>0.477611940298507</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.160703569778022</v>
+        <v>-0.160153402012799</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00577333671972338</v>
+        <v>0.00472982334854045</v>
       </c>
     </row>
     <row r="8">
@@ -866,16 +848,16 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.135643024090125</v>
+        <v>-0.144153434865446</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.784615384615385</v>
+        <v>-0.797802197802198</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -899,28 +881,28 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.135643024090125</v>
+        <v>-0.144153434865446</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.784615384615385</v>
+        <v>-0.797802197802198</v>
       </c>
       <c r="J9" t="n">
         <v>0.00497512437810945</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00497512437810945</v>
+        <v>0.0099502487562189</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.160044766611514</v>
+        <v>-0.159951406304208</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00274311124216874</v>
+        <v>0.00167682399869619</v>
       </c>
     </row>
     <row r="10">
@@ -940,7 +922,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -973,7 +955,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -985,16 +967,16 @@
         <v>-0.996690559042565</v>
       </c>
       <c r="J11" t="n">
-        <v>0.746268656716418</v>
+        <v>0.786069651741294</v>
       </c>
       <c r="K11" t="n">
-        <v>0.567164179104478</v>
+        <v>0.527363184079602</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.159997740293467</v>
+        <v>-0.158221597172258</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0266551547622026</v>
+        <v>0.0283946024649307</v>
       </c>
     </row>
     <row r="12">
@@ -1014,7 +996,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1047,7 +1029,7 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -1059,16 +1041,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.373134328358209</v>
+        <v>0.378109452736318</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.173319619383699</v>
+        <v>-0.173921264603411</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0143911414315295</v>
+        <v>0.00612203646134078</v>
       </c>
     </row>
   </sheetData>
@@ -1123,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.19531009887205</v>
+        <v>-0.200805565085166</v>
       </c>
     </row>
     <row r="5">
@@ -1134,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.168441652846996</v>
+        <v>-0.163046467953808</v>
       </c>
     </row>
     <row r="6">
@@ -1156,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.183398630967791</v>
+        <v>-0.171552566619878</v>
       </c>
     </row>
     <row r="8">
@@ -1178,7 +1160,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.193672317568487</v>
+        <v>-0.169414000686978</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.160016970042046</v>
+        <v>-0.159752712941319</v>
       </c>
     </row>
     <row r="17">
@@ -1266,7 +1248,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.167273359222998</v>
+        <v>-0.16248041688344</v>
       </c>
     </row>
     <row r="18">
@@ -1277,7 +1259,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.16027524142158</v>
+        <v>-0.173093640607219</v>
       </c>
     </row>
     <row r="19">
@@ -1288,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.169419696475528</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.159647830866043</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1358,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.190289203654055</v>
+        <v>-0.17287224251664</v>
       </c>
     </row>
     <row r="28">
@@ -1431,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.181093141500456</v>
+        <v>-0.177304415114782</v>
       </c>
     </row>
     <row r="33">
@@ -1453,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.166549569062147</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="35">
@@ -1464,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.159618641679663</v>
       </c>
     </row>
     <row r="36">
@@ -1497,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.164998211976526</v>
+        <v>-0.164403422775917</v>
       </c>
     </row>
     <row r="39">
@@ -1530,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.163835699809486</v>
+        <v>-0.167179471695331</v>
       </c>
     </row>
     <row r="42">
@@ -1585,7 +1567,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.161121702858989</v>
+        <v>-0.163894341800542</v>
       </c>
     </row>
     <row r="47">
@@ -1607,7 +1589,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.163191771523825</v>
+        <v>-0.163314664592637</v>
       </c>
     </row>
     <row r="49">
@@ -1618,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.163793733611949</v>
+        <v>-0.164635886265386</v>
       </c>
     </row>
     <row r="50">
@@ -1706,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.170736270332235</v>
+        <v>-0.164202652729426</v>
       </c>
     </row>
     <row r="58">
@@ -1750,7 +1732,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.166555623673286</v>
+        <v>-0.154566092662255</v>
       </c>
     </row>
     <row r="62">
@@ -2014,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.167466159543483</v>
+        <v>-0.168990861454462</v>
       </c>
     </row>
     <row r="86">
@@ -2025,7 +2007,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.159120634142465</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="87">
@@ -2058,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.179765272329138</v>
+        <v>-0.171259914689212</v>
       </c>
     </row>
     <row r="90">
@@ -2113,7 +2095,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.164070699212431</v>
+        <v>-0.162074512126161</v>
       </c>
     </row>
     <row r="95">
@@ -2190,7 +2172,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.129634987538587</v>
+        <v>-0.162242740036437</v>
       </c>
     </row>
     <row r="102">
@@ -2212,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.165549669115862</v>
+        <v>-0.168310318233441</v>
       </c>
     </row>
     <row r="104">
@@ -2223,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.166734911031918</v>
+        <v>-0.1648908276511</v>
       </c>
     </row>
     <row r="105">
@@ -2234,7 +2216,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.185307040340232</v>
+        <v>-0.179068716736298</v>
       </c>
     </row>
     <row r="106">
@@ -2300,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162266958906041</v>
       </c>
     </row>
     <row r="112">
@@ -2322,7 +2304,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.163856258360399</v>
       </c>
     </row>
     <row r="114">
@@ -2410,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.165971223526445</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="122">
@@ -2432,7 +2414,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.156923960922863</v>
+        <v>-0.156759504297677</v>
       </c>
     </row>
     <row r="124">
@@ -2443,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.178799166135599</v>
+        <v>-0.164677368860434</v>
       </c>
     </row>
     <row r="125">
@@ -2531,7 +2513,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164961263626959</v>
       </c>
     </row>
     <row r="133">
@@ -2564,7 +2546,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.163508916461917</v>
+        <v>-0.166480773237848</v>
       </c>
     </row>
     <row r="136">
@@ -2608,7 +2590,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.162561503842926</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="140">
@@ -2674,7 +2656,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.191830774512283</v>
+        <v>-0.176068177086105</v>
       </c>
     </row>
     <row r="146">
@@ -2685,7 +2667,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.12238577395519</v>
+        <v>-0.161759812014896</v>
       </c>
     </row>
     <row r="147">
@@ -2729,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.158805610985379</v>
+        <v>-0.131498568858693</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2733,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.168723745924277</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="153">
@@ -2784,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.160749569007245</v>
+        <v>-0.160802039654566</v>
       </c>
     </row>
     <row r="156">
@@ -2817,7 +2799,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.185391743635394</v>
+        <v>-0.202604109771136</v>
       </c>
     </row>
     <row r="159">
@@ -2839,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.165132166516575</v>
+        <v>-0.167061442106818</v>
       </c>
     </row>
     <row r="161">
@@ -2894,7 +2876,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.202299663660549</v>
+        <v>-0.209267921140138</v>
       </c>
     </row>
     <row r="166">
@@ -3015,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.0887453342177953</v>
+        <v>0.0168192063824665</v>
       </c>
     </row>
     <row r="177">
@@ -3026,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.173091125525846</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="178">
@@ -3059,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.160812782249538</v>
       </c>
     </row>
     <row r="181">
@@ -3081,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.156908587916508</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="183">
@@ -3114,7 +3096,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.174748096717336</v>
+        <v>-0.169289040977152</v>
       </c>
     </row>
     <row r="186">
@@ -3125,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.161169686154149</v>
+        <v>-0.17238927147764</v>
       </c>
     </row>
     <row r="187">
@@ -3158,7 +3140,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.154593954747095</v>
+        <v>-0.145237853673038</v>
       </c>
     </row>
     <row r="190">
@@ -3169,7 +3151,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.0846885855692228</v>
+        <v>-0.1618608539894</v>
       </c>
     </row>
     <row r="191">
@@ -3180,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.0337229620299329</v>
+        <v>-0.0917940490956426</v>
       </c>
     </row>
     <row r="192">
@@ -3290,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.193084605279751</v>
+        <v>-0.181918636778107</v>
       </c>
     </row>
     <row r="202">
@@ -3378,7 +3360,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.174458897469397</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="210">
@@ -3455,7 +3437,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.15529222420767</v>
       </c>
     </row>
     <row r="217">
@@ -3466,7 +3448,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.130184691673496</v>
+        <v>-0.151810298759581</v>
       </c>
     </row>
     <row r="218">
@@ -3477,7 +3459,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.172633393448842</v>
+        <v>-0.168173579370035</v>
       </c>
     </row>
     <row r="219">
@@ -3576,7 +3558,7 @@
         <v>16</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.160871386190482</v>
+        <v>-0.158612268579031</v>
       </c>
     </row>
     <row r="228">
@@ -3598,7 +3580,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.198288788799806</v>
+        <v>-0.182681128195045</v>
       </c>
     </row>
     <row r="230">
@@ -3664,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.0796648554193142</v>
+        <v>-0.0307495266376199</v>
       </c>
     </row>
     <row r="236">
@@ -3708,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.161848937116332</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="240">
@@ -3862,7 +3844,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.162441782775305</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="254">
@@ -3906,7 +3888,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.160076526664182</v>
       </c>
     </row>
     <row r="258">
@@ -3950,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.167491989563976</v>
+        <v>-0.160173266486413</v>
       </c>
     </row>
     <row r="262">
@@ -3994,7 +3976,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.17901569476147</v>
+        <v>-0.168508100742714</v>
       </c>
     </row>
     <row r="266">
@@ -4115,7 +4097,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.17869164898169</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="277">
@@ -4203,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161196844647325</v>
       </c>
     </row>
     <row r="285">
@@ -4214,7 +4196,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.25896921915941</v>
+        <v>-0.262783319635487</v>
       </c>
     </row>
     <row r="286">
@@ -4225,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.163207272675922</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="287">
@@ -4258,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.161662803863935</v>
+        <v>-0.168168099919039</v>
       </c>
     </row>
     <row r="290">
@@ -4379,7 +4361,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161474424580748</v>
       </c>
     </row>
     <row r="301">
@@ -4423,7 +4405,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.149539933226864</v>
+        <v>-0.149823196190985</v>
       </c>
     </row>
     <row r="305">
@@ -4522,7 +4504,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.160940766958284</v>
       </c>
     </row>
     <row r="314">
@@ -4533,7 +4515,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.16174796221913</v>
+        <v>-0.160636119069403</v>
       </c>
     </row>
     <row r="315">
@@ -4610,7 +4592,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.169277715862034</v>
+        <v>-0.168008055179221</v>
       </c>
     </row>
     <row r="322">
@@ -4632,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16181290146543</v>
       </c>
     </row>
     <row r="324">
@@ -4643,7 +4625,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.174047886505838</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="325">
@@ -4764,7 +4746,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.169427638111272</v>
+        <v>-0.166713886077414</v>
       </c>
     </row>
     <row r="336">
@@ -4808,7 +4790,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.16142865366941</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="340">
@@ -4841,7 +4823,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.163894926945341</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="343">
@@ -4874,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.173580174064132</v>
+        <v>-0.161861554603314</v>
       </c>
     </row>
     <row r="346">
@@ -4885,7 +4867,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.146450688392485</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="347">
@@ -4929,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.217959072112275</v>
+        <v>-0.218994239010251</v>
       </c>
     </row>
     <row r="351">
@@ -4984,7 +4966,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.160863034538047</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="356">
@@ -4995,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.170593423797541</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="357">
@@ -5017,7 +4999,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.27100305261531</v>
+        <v>-0.2447572854582</v>
       </c>
     </row>
     <row r="359">
@@ -5094,7 +5076,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.174983736073242</v>
+        <v>-0.178118841613417</v>
       </c>
     </row>
     <row r="366">
@@ -5127,7 +5109,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.197787082085735</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="369">
@@ -5182,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.171413404457862</v>
+        <v>-0.184330929667537</v>
       </c>
     </row>
     <row r="374">
@@ -5204,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.173996221592491</v>
+        <v>-0.180398542454267</v>
       </c>
     </row>
     <row r="376">
@@ -5215,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.188037834620568</v>
+        <v>-0.185062919177537</v>
       </c>
     </row>
     <row r="377">
@@ -5281,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.162962614016261</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="383">
@@ -5325,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162982592163997</v>
       </c>
     </row>
     <row r="387">
@@ -5369,7 +5351,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.165634551230514</v>
+        <v>-0.167394304782379</v>
       </c>
     </row>
     <row r="391">
@@ -5380,7 +5362,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.134074362522352</v>
+        <v>-0.164457278475183</v>
       </c>
     </row>
     <row r="392">
@@ -5479,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.168200023182118</v>
+        <v>-0.164412348570499</v>
       </c>
     </row>
     <row r="401">
@@ -5545,7 +5527,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164547751732892</v>
       </c>
     </row>
     <row r="407">
@@ -5578,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.161661885488092</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="410">
@@ -5666,7 +5648,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.142172325275029</v>
+        <v>-0.143165046540863</v>
       </c>
     </row>
     <row r="418">
@@ -5677,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.161635243251676</v>
+        <v>-0.165048308574338</v>
       </c>
     </row>
     <row r="419">
@@ -5776,7 +5758,7 @@
         <v>16</v>
       </c>
       <c r="C427" t="n">
-        <v>-0.158681700123052</v>
+        <v>-0.155272972310736</v>
       </c>
     </row>
     <row r="428">
@@ -5864,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.166487826298361</v>
+        <v>-0.13870604302577</v>
       </c>
     </row>
     <row r="436">
@@ -5897,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.159870298977698</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="439">
@@ -6040,7 +6022,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.160386976140323</v>
+        <v>-0.159034072934088</v>
       </c>
     </row>
     <row r="452">
@@ -6062,7 +6044,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.161045229617152</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="454">
@@ -6150,7 +6132,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.160524351648396</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="462">
@@ -6183,7 +6165,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.161001328808588</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="465">
@@ -6194,7 +6176,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.164562933359693</v>
+        <v>-0.152420115016181</v>
       </c>
     </row>
     <row r="466">
@@ -6315,7 +6297,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.160807342218988</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="477">
@@ -6414,7 +6396,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.194186020392991</v>
+        <v>-0.211446410040786</v>
       </c>
     </row>
     <row r="486">
@@ -6458,7 +6440,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167397517413739</v>
       </c>
     </row>
     <row r="490">
@@ -6623,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.163293828372253</v>
+        <v>-0.159664008076106</v>
       </c>
     </row>
     <row r="505">
@@ -6711,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.178914183933957</v>
+        <v>-0.161455314059816</v>
       </c>
     </row>
     <row r="513">
@@ -6722,7 +6704,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.160137451028679</v>
+        <v>-0.15951040439753</v>
       </c>
     </row>
     <row r="514">
@@ -6832,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.158448064152522</v>
       </c>
     </row>
     <row r="524">
@@ -6843,7 +6825,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.16077445856355</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="525">
@@ -6964,7 +6946,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.161502602750549</v>
+        <v>-0.161448641658227</v>
       </c>
     </row>
     <row r="536">
@@ -7030,7 +7012,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.166041907908092</v>
+        <v>-0.167140150117501</v>
       </c>
     </row>
     <row r="542">
@@ -7085,7 +7067,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.162680875620791</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="547">
@@ -7129,7 +7111,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164183954187035</v>
       </c>
     </row>
     <row r="551">
@@ -7195,7 +7177,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.223315783779626</v>
+        <v>-0.164227114472779</v>
       </c>
     </row>
     <row r="557">
@@ -7217,7 +7199,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.17492633326086</v>
+        <v>-0.162895683275675</v>
       </c>
     </row>
     <row r="559">
@@ -7393,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.157872030500712</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="575">
@@ -7404,7 +7386,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.177693941314075</v>
+        <v>-0.181870961130613</v>
       </c>
     </row>
     <row r="576">
@@ -7415,7 +7397,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.166469143960096</v>
+        <v>-0.16402462929225</v>
       </c>
     </row>
     <row r="577">
@@ -7569,7 +7551,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.172168678321791</v>
+        <v>-0.176074977014389</v>
       </c>
     </row>
     <row r="591">
@@ -7679,7 +7661,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.162846020251437</v>
+        <v>-0.15482844065066</v>
       </c>
     </row>
     <row r="601">
@@ -7723,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.160368128171568</v>
+        <v>-0.163274176991554</v>
       </c>
     </row>
     <row r="605">
@@ -7756,7 +7738,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.160828208627606</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="608">
@@ -7976,7 +7958,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.158944199190273</v>
+        <v>-0.159797005381116</v>
       </c>
     </row>
     <row r="628">
@@ -8064,7 +8046,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.173944940834696</v>
+        <v>-0.164931275880276</v>
       </c>
     </row>
     <row r="636">
@@ -8130,7 +8112,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.187712398990441</v>
+        <v>-0.176331108395313</v>
       </c>
     </row>
     <row r="642">
@@ -8207,7 +8189,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.158032956764219</v>
+        <v>-0.153874620365273</v>
       </c>
     </row>
     <row r="649">
@@ -8713,7 +8695,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.163641796570677</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="695">
@@ -8867,7 +8849,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.152353496873582</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="709">
@@ -8988,7 +8970,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.156130916456264</v>
+        <v>-0.159525724485696</v>
       </c>
     </row>
     <row r="720">
@@ -9406,7 +9388,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.165290884685341</v>
+        <v>-0.163710620655009</v>
       </c>
     </row>
     <row r="758">
@@ -9659,7 +9641,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.158391980678255</v>
       </c>
     </row>
     <row r="781">
@@ -9824,7 +9806,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.169866807869063</v>
+        <v>-0.171897030118018</v>
       </c>
     </row>
     <row r="796">
@@ -9868,7 +9850,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.175058653524857</v>
+        <v>-0.16646842791509</v>
       </c>
     </row>
     <row r="800">
@@ -9890,7 +9872,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.151040288773813</v>
+        <v>-0.15681301778664</v>
       </c>
     </row>
     <row r="802">
@@ -9901,7 +9883,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.163551348376284</v>
+        <v>-0.160920286936208</v>
       </c>
     </row>
     <row r="803">
@@ -9945,7 +9927,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.176941436703288</v>
+        <v>-0.173287406762846</v>
       </c>
     </row>
     <row r="807">
@@ -9967,7 +9949,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.164202887267104</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="809">
@@ -10022,7 +10004,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.148554435598142</v>
+        <v>-0.153277238193441</v>
       </c>
     </row>
     <row r="814">
@@ -10044,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.166002483404474</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="816">
@@ -10077,7 +10059,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.169364838270547</v>
+        <v>-0.167349350093566</v>
       </c>
     </row>
     <row r="819">
@@ -10110,7 +10092,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.0446478585803778</v>
+        <v>0.0503583658787374</v>
       </c>
     </row>
     <row r="822">
@@ -10154,7 +10136,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.229590373540716</v>
+        <v>-0.17260902747508</v>
       </c>
     </row>
     <row r="826">
@@ -10187,7 +10169,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.038580474495217</v>
+        <v>0.0256590751183214</v>
       </c>
     </row>
     <row r="829">
@@ -10264,7 +10246,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.0950799682812682</v>
+        <v>-0.158876471616807</v>
       </c>
     </row>
     <row r="836">
@@ -10286,7 +10268,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.162228639383518</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="838">
@@ -10429,7 +10411,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.181388262215068</v>
       </c>
     </row>
     <row r="851">
@@ -10473,7 +10455,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.161127437812945</v>
+        <v>-0.194497995633945</v>
       </c>
     </row>
     <row r="855">
@@ -10517,7 +10499,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.165019511215501</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="859">
@@ -10528,7 +10510,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.167468878299457</v>
+        <v>-0.169522565432484</v>
       </c>
     </row>
     <row r="860">
@@ -10583,7 +10565,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.164220659471623</v>
+        <v>-0.161176749657087</v>
       </c>
     </row>
     <row r="865">
@@ -10616,7 +10598,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.168313457867129</v>
+        <v>-0.16663564476488</v>
       </c>
     </row>
     <row r="868">
@@ -10671,7 +10653,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.183143529678127</v>
+        <v>-0.191082334373904</v>
       </c>
     </row>
     <row r="873">
@@ -10781,7 +10763,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.178888690042332</v>
+        <v>-0.180907455675528</v>
       </c>
     </row>
     <row r="883">
@@ -10814,7 +10796,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.160800445372501</v>
       </c>
     </row>
     <row r="886">
@@ -10836,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.184730513700599</v>
+        <v>-0.16935852471062</v>
       </c>
     </row>
     <row r="888">
@@ -10847,7 +10829,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.162233442782928</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="889">
@@ -10891,7 +10873,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.144051516864141</v>
+        <v>-0.161833511650256</v>
       </c>
     </row>
     <row r="893">
@@ -10902,7 +10884,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.165381451945386</v>
+        <v>-0.152076032600806</v>
       </c>
     </row>
     <row r="894">
@@ -10957,7 +10939,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.161636120299119</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="899">
@@ -11001,7 +10983,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.186237128376915</v>
+        <v>-0.180287844367865</v>
       </c>
     </row>
     <row r="903">
@@ -11045,7 +11027,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.163688735823211</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="907">
@@ -11067,7 +11049,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.172758058423021</v>
+        <v>-0.185373394615347</v>
       </c>
     </row>
     <row r="909">
@@ -11111,7 +11093,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.16597425715031</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="913">
@@ -11133,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.176922296632775</v>
+        <v>-0.190982013699038</v>
       </c>
     </row>
     <row r="915">
@@ -11144,7 +11126,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.14346656100334</v>
+        <v>-0.136801700543934</v>
       </c>
     </row>
     <row r="916">
@@ -11155,7 +11137,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.251960610593038</v>
+        <v>-0.197902561318097</v>
       </c>
     </row>
     <row r="917">
@@ -11166,7 +11148,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.161449749360508</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="918">
@@ -11210,7 +11192,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.160541785626283</v>
+        <v>-0.159108419206038</v>
       </c>
     </row>
     <row r="922">
@@ -11232,7 +11214,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.19894368452316</v>
+        <v>-0.178077046186547</v>
       </c>
     </row>
     <row r="924">
@@ -11254,7 +11236,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.154009722873512</v>
+        <v>-0.157837879961427</v>
       </c>
     </row>
     <row r="926">
@@ -11320,7 +11302,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.176997711765833</v>
+        <v>-0.167808881575201</v>
       </c>
     </row>
     <row r="932">
@@ -11342,7 +11324,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.159957310780922</v>
       </c>
     </row>
     <row r="934">
@@ -11353,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.161512493009081</v>
+        <v>-0.165864081085552</v>
       </c>
     </row>
     <row r="935">
@@ -11386,7 +11368,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.201951790492814</v>
+        <v>-0.190331289886129</v>
       </c>
     </row>
     <row r="938">
@@ -11397,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.171067224210051</v>
       </c>
     </row>
     <row r="939">
@@ -11419,7 +11401,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.180584745311922</v>
+        <v>-0.187374536807685</v>
       </c>
     </row>
     <row r="941">
@@ -11452,7 +11434,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.181322928549577</v>
+        <v>-0.162432922343331</v>
       </c>
     </row>
     <row r="944">
@@ -11474,7 +11456,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.0399105583567596</v>
+        <v>-0.0193267345081272</v>
       </c>
     </row>
     <row r="946">
@@ -11507,7 +11489,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.183304904484358</v>
+        <v>-0.181506854617434</v>
       </c>
     </row>
     <row r="949">
@@ -11606,7 +11588,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.180483545657361</v>
+        <v>-0.160366772191485</v>
       </c>
     </row>
     <row r="958">
@@ -11639,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.19661718660554</v>
+        <v>-0.145076249655725</v>
       </c>
     </row>
     <row r="961">
@@ -11672,7 +11654,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.163814738369535</v>
+        <v>-0.162984936722644</v>
       </c>
     </row>
     <row r="964">
@@ -11727,7 +11709,7 @@
         <v>16</v>
       </c>
       <c r="C968" t="n">
-        <v>0.0925467364791079</v>
+        <v>0.0643559963104586</v>
       </c>
     </row>
     <row r="969">
@@ -11782,7 +11764,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.192344104837098</v>
+        <v>-0.179006641979033</v>
       </c>
     </row>
     <row r="974">
@@ -11815,7 +11797,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.17983197302076</v>
+        <v>-0.174890167475875</v>
       </c>
     </row>
     <row r="977">
@@ -11870,7 +11852,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.167854290838826</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="982">
@@ -11892,7 +11874,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.161539897101436</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="984">
@@ -11925,7 +11907,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.230198964848882</v>
+        <v>-0.186617075303495</v>
       </c>
     </row>
     <row r="987">
@@ -11947,7 +11929,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.161664669773446</v>
+        <v>-0.163216048697873</v>
       </c>
     </row>
     <row r="989">
@@ -11991,7 +11973,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.168586089825653</v>
+        <v>-0.167397140736199</v>
       </c>
     </row>
     <row r="993">
@@ -12024,7 +12006,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.160315841332615</v>
       </c>
     </row>
     <row r="996">
@@ -12079,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.177454557465565</v>
+        <v>-0.173395016537827</v>
       </c>
     </row>
     <row r="1001">
@@ -12112,7 +12094,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.173041674588241</v>
+        <v>-0.174105267168692</v>
       </c>
     </row>
     <row r="1004">
@@ -12156,7 +12138,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.244362138371332</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1008">
@@ -12222,7 +12204,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.159352511865808</v>
+        <v>-0.117712463072271</v>
       </c>
     </row>
     <row r="1014">
@@ -12266,7 +12248,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.176283828660046</v>
+        <v>-0.177874588295649</v>
       </c>
     </row>
     <row r="1018">
@@ -12288,7 +12270,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.14887200570381</v>
+        <v>-0.162521267884991</v>
       </c>
     </row>
     <row r="1020">
@@ -12321,7 +12303,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.174039066039003</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1023">
@@ -12343,7 +12325,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.187331736299129</v>
+        <v>-0.189288933759271</v>
       </c>
     </row>
     <row r="1025">
@@ -12431,7 +12413,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.169227102293758</v>
+        <v>-0.171832077590344</v>
       </c>
     </row>
     <row r="1033">
@@ -12442,7 +12424,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.172810135822617</v>
       </c>
     </row>
     <row r="1034">
@@ -12475,7 +12457,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.214854704813673</v>
+        <v>-0.183844307960923</v>
       </c>
     </row>
     <row r="1037">
@@ -12508,7 +12490,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.175327222745952</v>
+        <v>-0.180705010100618</v>
       </c>
     </row>
     <row r="1040">
@@ -12563,7 +12545,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.174410417945903</v>
+        <v>-0.175330420326797</v>
       </c>
     </row>
     <row r="1045">
@@ -12717,7 +12699,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.188693990280211</v>
+        <v>-0.191034343769085</v>
       </c>
     </row>
     <row r="1059">
@@ -12761,7 +12743,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.178627986442833</v>
+        <v>-0.1813344280885</v>
       </c>
     </row>
     <row r="1063">
@@ -12849,7 +12831,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.180816512633331</v>
       </c>
     </row>
     <row r="1071">
@@ -12992,7 +12974,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.170905430265529</v>
+        <v>-0.172953311598648</v>
       </c>
     </row>
     <row r="1084">
@@ -13124,7 +13106,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.183545192016294</v>
+        <v>-0.183476223496354</v>
       </c>
     </row>
     <row r="1096">
@@ -13146,7 +13128,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.17598133400554</v>
+        <v>-0.20566843590542</v>
       </c>
     </row>
     <row r="1098">
@@ -13256,7 +13238,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.174284401479087</v>
+        <v>-0.173788150213204</v>
       </c>
     </row>
     <row r="1108">
@@ -13289,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.162544150638381</v>
+        <v>-0.162224026721181</v>
       </c>
     </row>
     <row r="1111">
@@ -13333,7 +13315,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.00428584839059631</v>
+        <v>-0.157737539143586</v>
       </c>
     </row>
     <row r="1115">
@@ -13355,7 +13337,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.171863744483656</v>
       </c>
     </row>
     <row r="1117">
@@ -13421,7 +13403,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.17913994630101</v>
+        <v>-0.174556188728449</v>
       </c>
     </row>
     <row r="1123">
@@ -13443,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.179929369873561</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1125">
@@ -13454,7 +13436,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.177642869339222</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1126">
@@ -13520,7 +13502,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.174725389499227</v>
+        <v>-0.172299780865395</v>
       </c>
     </row>
     <row r="1132">
@@ -13542,7 +13524,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.182187745412907</v>
+        <v>-0.178546990282566</v>
       </c>
     </row>
     <row r="1134">
@@ -13619,7 +13601,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.176366452566207</v>
+        <v>-0.180552632551281</v>
       </c>
     </row>
     <row r="1141">
@@ -13718,7 +13700,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.158903814495247</v>
+        <v>-0.163570273312613</v>
       </c>
     </row>
     <row r="1150">
@@ -13729,7 +13711,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.173783895331862</v>
+        <v>-0.176698884384314</v>
       </c>
     </row>
     <row r="1151">
@@ -13762,7 +13744,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.177670887593703</v>
+        <v>-0.191836755799412</v>
       </c>
     </row>
     <row r="1154">
@@ -13872,7 +13854,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.160701250508919</v>
+        <v>-0.149700515794171</v>
       </c>
     </row>
     <row r="1164">
@@ -13949,7 +13931,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.174295207337709</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1171">
@@ -13993,7 +13975,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.119484379777278</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1175">
@@ -14070,7 +14052,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.177153903453113</v>
       </c>
     </row>
     <row r="1182">
@@ -14092,7 +14074,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.18327770794834</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1184">
@@ -14114,7 +14096,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.170562396060129</v>
+        <v>-0.177989180234044</v>
       </c>
     </row>
     <row r="1186">
@@ -14125,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.191046912226707</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1187">
@@ -14169,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.192024352729793</v>
+        <v>-0.188840866928551</v>
       </c>
     </row>
     <row r="1191">
@@ -14191,7 +14173,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.172507402540351</v>
       </c>
     </row>
     <row r="1193">
@@ -14224,7 +14206,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.174712514708485</v>
+        <v>-0.177446653968706</v>
       </c>
     </row>
     <row r="1196">
@@ -14279,7 +14261,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.182886931073224</v>
+        <v>-0.196187259359743</v>
       </c>
     </row>
     <row r="1201">
@@ -15049,7 +15031,7 @@
         <v>1.706</v>
       </c>
       <c r="E44" t="n">
-        <v>1.81014569176236</v>
+        <v>1.84187168048285</v>
       </c>
     </row>
     <row r="45">
@@ -15066,7 +15048,7 @@
         <v>4.218</v>
       </c>
       <c r="E45" t="n">
-        <v>1.58197047271898</v>
+        <v>1.60460690730092</v>
       </c>
     </row>
     <row r="46">
@@ -15083,7 +15065,7 @@
         <v>1.578</v>
       </c>
       <c r="E46" t="n">
-        <v>1.81511882243404</v>
+        <v>1.8413311327557</v>
       </c>
     </row>
     <row r="47">
@@ -15117,7 +15099,7 @@
         <v>2.983</v>
       </c>
       <c r="E48" t="n">
-        <v>1.97545717062633</v>
+        <v>2.08899548532443</v>
       </c>
     </row>
     <row r="49">
@@ -15134,7 +15116,7 @@
         <v>2.44</v>
       </c>
       <c r="E49" t="n">
-        <v>1.82025991282719</v>
+        <v>1.79215384615385</v>
       </c>
     </row>
     <row r="50">
@@ -15168,7 +15150,7 @@
         <v>-1.918</v>
       </c>
       <c r="E51" t="n">
-        <v>2.03334993564162</v>
+        <v>2.09957415423014</v>
       </c>
     </row>
     <row r="52">
@@ -15185,7 +15167,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>1.88130252841165</v>
+        <v>1.92815384615385</v>
       </c>
     </row>
     <row r="53">
@@ -15236,7 +15218,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>1.95716470654344</v>
+        <v>1.96592307692308</v>
       </c>
     </row>
     <row r="56">
@@ -15253,7 +15235,7 @@
         <v>1.311</v>
       </c>
       <c r="E56" t="n">
-        <v>1.87943366448874</v>
+        <v>1.87636453898504</v>
       </c>
     </row>
     <row r="57">
@@ -15270,7 +15252,7 @@
         <v>2.862</v>
       </c>
       <c r="E57" t="n">
-        <v>1.75536937189779</v>
+        <v>1.76079526163046</v>
       </c>
     </row>
     <row r="58">
@@ -16323,13 +16305,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D35" t="n">
         <v>14</v>
@@ -16340,13 +16322,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
@@ -16357,13 +16339,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
         <v>14</v>
@@ -16374,13 +16356,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
         <v>14</v>
@@ -16391,13 +16373,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>14</v>
@@ -16408,13 +16390,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
         <v>14</v>
@@ -16431,7 +16413,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D41" t="n">
         <v>14</v>
@@ -16448,7 +16430,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D42" t="n">
         <v>14</v>
@@ -16465,7 +16447,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>14</v>
@@ -16482,7 +16464,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D44" t="n">
         <v>14</v>
@@ -16499,7 +16481,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
         <v>14</v>
@@ -16516,7 +16498,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D46" t="n">
         <v>14</v>
@@ -16533,7 +16515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D47" t="n">
         <v>14</v>
@@ -16550,7 +16532,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D48" t="n">
         <v>14</v>
@@ -16567,7 +16549,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D49" t="n">
         <v>14</v>
@@ -16584,7 +16566,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D50" t="n">
         <v>14</v>
@@ -16601,7 +16583,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D51" t="n">
         <v>14</v>
@@ -16618,7 +16600,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D52" t="n">
         <v>14</v>
@@ -16635,7 +16617,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
         <v>14</v>
@@ -16652,7 +16634,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D54" t="n">
         <v>14</v>
@@ -16669,7 +16651,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D55" t="n">
         <v>14</v>
@@ -16686,7 +16668,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D56" t="n">
         <v>14</v>
@@ -16703,7 +16685,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D57" t="n">
         <v>14</v>
@@ -16720,7 +16702,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D58" t="n">
         <v>14</v>
@@ -16737,7 +16719,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D59" t="n">
         <v>14</v>
@@ -16754,7 +16736,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D60" t="n">
         <v>14</v>
@@ -16771,7 +16753,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D61" t="n">
         <v>14</v>
@@ -16788,7 +16770,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D62" t="n">
         <v>14</v>
@@ -16805,7 +16787,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D63" t="n">
         <v>14</v>
@@ -16822,7 +16804,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D64" t="n">
         <v>14</v>
@@ -16839,7 +16821,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D65" t="n">
         <v>14</v>
@@ -16856,7 +16838,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D66" t="n">
         <v>14</v>
@@ -16873,7 +16855,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
@@ -16884,13 +16866,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s">
         <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D68" t="n">
         <v>14</v>
@@ -16901,13 +16883,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B69" t="s">
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D69" t="n">
         <v>14</v>
@@ -16918,13 +16900,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D70" t="n">
         <v>14</v>
@@ -16935,13 +16917,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
         <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D71" t="n">
         <v>14</v>
@@ -16952,13 +16934,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D72" t="n">
         <v>14</v>
@@ -16969,13 +16951,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D73" t="n">
         <v>14</v>
@@ -16986,13 +16968,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
         <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D74" t="n">
         <v>14</v>
@@ -17003,13 +16985,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B75" t="s">
         <v>16</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D75" t="n">
         <v>14</v>
@@ -17020,13 +17002,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s">
         <v>16</v>
       </c>
       <c r="C76" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D76" t="n">
         <v>14</v>
@@ -17037,13 +17019,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B77" t="s">
         <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="D77" t="n">
         <v>14</v>
@@ -17054,13 +17036,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B78" t="s">
         <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D78" t="n">
         <v>14</v>
@@ -17071,13 +17053,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B79" t="s">
         <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D79" t="n">
         <v>14</v>
@@ -17094,7 +17076,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D80" t="n">
         <v>14</v>
@@ -17111,7 +17093,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D81" t="n">
         <v>14</v>
@@ -17128,7 +17110,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D82" t="n">
         <v>14</v>
@@ -17145,7 +17127,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D83" t="n">
         <v>14</v>
@@ -17162,7 +17144,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D84" t="n">
         <v>14</v>
@@ -17179,7 +17161,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D85" t="n">
         <v>14</v>
@@ -17196,7 +17178,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D86" t="n">
         <v>14</v>
@@ -17213,7 +17195,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D87" t="n">
         <v>14</v>
@@ -17230,7 +17212,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D88" t="n">
         <v>14</v>
@@ -17247,7 +17229,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D89" t="n">
         <v>14</v>
@@ -17264,7 +17246,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D90" t="n">
         <v>14</v>
@@ -17281,7 +17263,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D91" t="n">
         <v>14</v>
@@ -17298,7 +17280,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D92" t="n">
         <v>14</v>
@@ -17315,7 +17297,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D93" t="n">
         <v>14</v>
@@ -17332,7 +17314,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D94" t="n">
         <v>14</v>
@@ -17349,7 +17331,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D95" t="n">
         <v>14</v>
@@ -17366,7 +17348,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D96" t="n">
         <v>14</v>
@@ -17383,7 +17365,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D97" t="n">
         <v>14</v>
@@ -17400,7 +17382,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D98" t="n">
         <v>14</v>
@@ -17417,7 +17399,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D99" t="n">
         <v>14</v>
@@ -17434,7 +17416,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D100" t="n">
         <v>14</v>
@@ -17445,13 +17427,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D101" t="n">
         <v>14</v>
@@ -17462,13 +17444,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B102" t="s">
         <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D102" t="n">
         <v>14</v>
@@ -17479,13 +17461,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B103" t="s">
         <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D103" t="n">
         <v>14</v>
@@ -17496,13 +17478,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s">
         <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D104" t="n">
         <v>14</v>
@@ -17513,13 +17495,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B105" t="s">
         <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D105" t="n">
         <v>14</v>
@@ -17530,13 +17512,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B106" t="s">
         <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D106" t="n">
         <v>14</v>
@@ -17547,13 +17529,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B107" t="s">
         <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D107" t="n">
         <v>14</v>
@@ -17564,13 +17546,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B108" t="s">
         <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D108" t="n">
         <v>14</v>
@@ -17581,13 +17563,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B109" t="s">
         <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D109" t="n">
         <v>14</v>
@@ -17598,13 +17580,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D110" t="n">
         <v>14</v>
@@ -17615,13 +17597,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B111" t="s">
         <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D111" t="n">
         <v>14</v>
@@ -17632,13 +17614,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B112" t="s">
         <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D112" t="n">
         <v>14</v>
@@ -17649,13 +17631,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B113" t="s">
         <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D113" t="n">
         <v>14</v>
@@ -17666,13 +17648,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B114" t="s">
         <v>16</v>
       </c>
       <c r="C114" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D114" t="n">
         <v>14</v>
@@ -17683,13 +17665,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
       </c>
       <c r="C115" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D115" t="n">
         <v>14</v>
@@ -17700,13 +17682,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D116" t="n">
         <v>14</v>
@@ -17717,13 +17699,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B117" t="s">
         <v>16</v>
       </c>
       <c r="C117" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D117" t="n">
         <v>14</v>
@@ -17734,13 +17716,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B118" t="s">
         <v>16</v>
       </c>
       <c r="C118" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D118" t="n">
         <v>14</v>
@@ -17757,7 +17739,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D119" t="n">
         <v>14</v>
@@ -17774,7 +17756,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D120" t="n">
         <v>14</v>
@@ -17791,7 +17773,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D121" t="n">
         <v>14</v>
@@ -17808,7 +17790,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D122" t="n">
         <v>14</v>
@@ -17825,7 +17807,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D123" t="n">
         <v>14</v>
@@ -17842,7 +17824,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D124" t="n">
         <v>14</v>
@@ -17859,7 +17841,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D125" t="n">
         <v>14</v>
@@ -17876,7 +17858,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D126" t="n">
         <v>14</v>
@@ -17893,7 +17875,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D127" t="n">
         <v>14</v>
@@ -17910,7 +17892,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D128" t="n">
         <v>14</v>
@@ -17927,7 +17909,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D129" t="n">
         <v>14</v>
@@ -17944,7 +17926,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D130" t="n">
         <v>14</v>
@@ -17961,7 +17943,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D131" t="n">
         <v>14</v>
@@ -17978,7 +17960,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D132" t="n">
         <v>14</v>
@@ -17995,7 +17977,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D133" t="n">
         <v>14</v>
@@ -18006,13 +17988,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B134" t="s">
         <v>16</v>
       </c>
       <c r="C134" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D134" t="n">
         <v>14</v>
@@ -18023,13 +18005,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B135" t="s">
         <v>16</v>
       </c>
       <c r="C135" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D135" t="n">
         <v>14</v>
@@ -18040,13 +18022,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B136" t="s">
         <v>16</v>
       </c>
       <c r="C136" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D136" t="n">
         <v>14</v>
@@ -18057,13 +18039,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B137" t="s">
         <v>16</v>
       </c>
       <c r="C137" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D137" t="n">
         <v>14</v>
@@ -18074,13 +18056,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B138" t="s">
         <v>16</v>
       </c>
       <c r="C138" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D138" t="n">
         <v>14</v>
@@ -18091,13 +18073,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B139" t="s">
         <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D139" t="n">
         <v>14</v>
@@ -18108,13 +18090,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B140" t="s">
         <v>16</v>
       </c>
       <c r="C140" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D140" t="n">
         <v>14</v>
@@ -18125,13 +18107,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B141" t="s">
         <v>16</v>
       </c>
       <c r="C141" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D141" t="n">
         <v>14</v>
@@ -18142,13 +18124,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D142" t="n">
         <v>14</v>
@@ -18159,13 +18141,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B143" t="s">
         <v>16</v>
       </c>
       <c r="C143" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D143" t="n">
         <v>14</v>
@@ -18176,13 +18158,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B144" t="s">
         <v>16</v>
       </c>
       <c r="C144" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D144" t="n">
         <v>14</v>
@@ -18193,13 +18175,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B145" t="s">
         <v>16</v>
       </c>
       <c r="C145" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D145" t="n">
         <v>14</v>
@@ -18210,13 +18192,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
         <v>16</v>
       </c>
       <c r="C146" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D146" t="n">
         <v>14</v>
@@ -18227,13 +18209,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
         <v>16</v>
       </c>
       <c r="C147" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D147" t="n">
         <v>14</v>
@@ -18244,13 +18226,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B148" t="s">
         <v>16</v>
       </c>
       <c r="C148" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D148" t="n">
         <v>14</v>
@@ -18261,13 +18243,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
       </c>
       <c r="C149" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D149" t="n">
         <v>14</v>
@@ -18278,13 +18260,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B150" t="s">
         <v>16</v>
       </c>
       <c r="C150" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D150" t="n">
         <v>14</v>
@@ -18295,13 +18277,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
         <v>16</v>
       </c>
       <c r="C151" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D151" t="n">
         <v>14</v>
@@ -18312,13 +18294,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B152" t="s">
         <v>16</v>
       </c>
       <c r="C152" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D152" t="n">
         <v>14</v>
@@ -18329,13 +18311,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B153" t="s">
         <v>16</v>
       </c>
       <c r="C153" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D153" t="n">
         <v>14</v>
@@ -18346,13 +18328,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B154" t="s">
         <v>16</v>
       </c>
       <c r="C154" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D154" t="n">
         <v>14</v>
@@ -18363,13 +18345,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B155" t="s">
         <v>16</v>
       </c>
       <c r="C155" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D155" t="n">
         <v>14</v>
@@ -18380,13 +18362,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B156" t="s">
         <v>16</v>
       </c>
       <c r="C156" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D156" t="n">
         <v>14</v>
@@ -18397,13 +18379,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B157" t="s">
         <v>16</v>
       </c>
       <c r="C157" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D157" t="n">
         <v>14</v>
@@ -18420,7 +18402,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D158" t="n">
         <v>14</v>
@@ -18437,7 +18419,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D159" t="n">
         <v>14</v>
@@ -18454,7 +18436,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D160" t="n">
         <v>14</v>
@@ -18471,7 +18453,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D161" t="n">
         <v>14</v>
@@ -18488,7 +18470,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D162" t="n">
         <v>14</v>
@@ -18505,7 +18487,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D163" t="n">
         <v>14</v>
@@ -18522,7 +18504,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D164" t="n">
         <v>14</v>
@@ -18539,7 +18521,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D165" t="n">
         <v>14</v>
@@ -18556,7 +18538,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D166" t="n">
         <v>14</v>
@@ -18567,16 +18549,16 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B167" t="s">
         <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D167" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -18584,16 +18566,16 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B168" t="s">
         <v>16</v>
       </c>
       <c r="C168" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D168" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
@@ -18601,16 +18583,16 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B169" t="s">
         <v>16</v>
       </c>
       <c r="C169" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D169" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E169" t="n">
         <v>1</v>
@@ -18618,16 +18600,16 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B170" t="s">
         <v>16</v>
       </c>
       <c r="C170" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -18635,16 +18617,16 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B171" t="s">
         <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D171" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E171" t="n">
         <v>1</v>
@@ -18652,16 +18634,16 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B172" t="s">
         <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D172" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -18669,16 +18651,16 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B173" t="s">
         <v>16</v>
       </c>
       <c r="C173" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D173" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -18686,16 +18668,16 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B174" t="s">
         <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D174" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
@@ -18703,16 +18685,16 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B175" t="s">
         <v>16</v>
       </c>
       <c r="C175" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D175" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E175" t="n">
         <v>1</v>
@@ -18720,16 +18702,16 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B176" t="s">
         <v>16</v>
       </c>
       <c r="C176" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D176" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -18737,16 +18719,16 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B177" t="s">
         <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D177" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E177" t="n">
         <v>1</v>
@@ -18754,16 +18736,16 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B178" t="s">
         <v>16</v>
       </c>
       <c r="C178" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D178" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -18771,16 +18753,16 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B179" t="s">
         <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D179" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E179" t="n">
         <v>1</v>
@@ -18788,16 +18770,16 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B180" t="s">
         <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D180" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E180" t="n">
         <v>1</v>
@@ -18805,16 +18787,16 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B181" t="s">
         <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D181" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
@@ -18822,16 +18804,16 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B182" t="s">
         <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D182" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E182" t="n">
         <v>1</v>
@@ -18839,16 +18821,16 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B183" t="s">
         <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D183" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E183" t="n">
         <v>1</v>
@@ -18856,16 +18838,16 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B184" t="s">
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D184" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E184" t="n">
         <v>1</v>
@@ -18873,16 +18855,16 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B185" t="s">
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D185" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
@@ -18890,16 +18872,16 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B186" t="s">
         <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D186" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
@@ -18907,16 +18889,16 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B187" t="s">
         <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D187" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E187" t="n">
         <v>1</v>
@@ -18924,16 +18906,16 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B188" t="s">
         <v>16</v>
       </c>
       <c r="C188" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D188" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -18941,16 +18923,16 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B189" t="s">
         <v>16</v>
       </c>
       <c r="C189" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D189" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E189" t="n">
         <v>1</v>
@@ -18958,16 +18940,16 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D190" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E190" t="n">
         <v>1</v>
@@ -18975,16 +18957,16 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B191" t="s">
         <v>16</v>
       </c>
       <c r="C191" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D191" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E191" t="n">
         <v>1</v>
@@ -18992,16 +18974,16 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B192" t="s">
         <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D192" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E192" t="n">
         <v>1</v>
@@ -19009,16 +18991,16 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B193" t="s">
         <v>16</v>
       </c>
       <c r="C193" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D193" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E193" t="n">
         <v>1</v>
@@ -19026,16 +19008,16 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
       </c>
       <c r="C194" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D194" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -19043,16 +19025,16 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
       </c>
       <c r="C195" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D195" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E195" t="n">
         <v>1</v>
@@ -19060,16 +19042,16 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D196" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
@@ -19083,7 +19065,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D197" t="n">
         <v>13</v>
@@ -19100,7 +19082,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D198" t="n">
         <v>13</v>
@@ -19117,624 +19099,12 @@
         <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D199" t="n">
         <v>13</v>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>21</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="s">
-        <v>45</v>
-      </c>
-      <c r="D200" t="n">
-        <v>13</v>
-      </c>
-      <c r="E200" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>21</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="s">
-        <v>46</v>
-      </c>
-      <c r="D201" t="n">
-        <v>13</v>
-      </c>
-      <c r="E201" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>21</v>
-      </c>
-      <c r="B202" t="s">
-        <v>16</v>
-      </c>
-      <c r="C202" t="s">
-        <v>47</v>
-      </c>
-      <c r="D202" t="n">
-        <v>13</v>
-      </c>
-      <c r="E202" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>21</v>
-      </c>
-      <c r="B203" t="s">
-        <v>16</v>
-      </c>
-      <c r="C203" t="s">
-        <v>48</v>
-      </c>
-      <c r="D203" t="n">
-        <v>13</v>
-      </c>
-      <c r="E203" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s">
-        <v>21</v>
-      </c>
-      <c r="B204" t="s">
-        <v>16</v>
-      </c>
-      <c r="C204" t="s">
-        <v>49</v>
-      </c>
-      <c r="D204" t="n">
-        <v>13</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>21</v>
-      </c>
-      <c r="B205" t="s">
-        <v>16</v>
-      </c>
-      <c r="C205" t="s">
-        <v>50</v>
-      </c>
-      <c r="D205" t="n">
-        <v>13</v>
-      </c>
-      <c r="E205" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s">
-        <v>21</v>
-      </c>
-      <c r="B206" t="s">
-        <v>16</v>
-      </c>
-      <c r="C206" t="s">
-        <v>51</v>
-      </c>
-      <c r="D206" t="n">
-        <v>13</v>
-      </c>
-      <c r="E206" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>21</v>
-      </c>
-      <c r="B207" t="s">
-        <v>16</v>
-      </c>
-      <c r="C207" t="s">
-        <v>52</v>
-      </c>
-      <c r="D207" t="n">
-        <v>13</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s">
-        <v>21</v>
-      </c>
-      <c r="B208" t="s">
-        <v>16</v>
-      </c>
-      <c r="C208" t="s">
-        <v>53</v>
-      </c>
-      <c r="D208" t="n">
-        <v>13</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s">
-        <v>21</v>
-      </c>
-      <c r="B209" t="s">
-        <v>16</v>
-      </c>
-      <c r="C209" t="s">
-        <v>54</v>
-      </c>
-      <c r="D209" t="n">
-        <v>13</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>21</v>
-      </c>
-      <c r="B210" t="s">
-        <v>16</v>
-      </c>
-      <c r="C210" t="s">
-        <v>55</v>
-      </c>
-      <c r="D210" t="n">
-        <v>13</v>
-      </c>
-      <c r="E210" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>21</v>
-      </c>
-      <c r="B211" t="s">
-        <v>16</v>
-      </c>
-      <c r="C211" t="s">
-        <v>56</v>
-      </c>
-      <c r="D211" t="n">
-        <v>13</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>21</v>
-      </c>
-      <c r="B212" t="s">
-        <v>16</v>
-      </c>
-      <c r="C212" t="s">
-        <v>57</v>
-      </c>
-      <c r="D212" t="n">
-        <v>13</v>
-      </c>
-      <c r="E212" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>21</v>
-      </c>
-      <c r="B213" t="s">
-        <v>16</v>
-      </c>
-      <c r="C213" t="s">
-        <v>58</v>
-      </c>
-      <c r="D213" t="n">
-        <v>13</v>
-      </c>
-      <c r="E213" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>21</v>
-      </c>
-      <c r="B214" t="s">
-        <v>16</v>
-      </c>
-      <c r="C214" t="s">
-        <v>59</v>
-      </c>
-      <c r="D214" t="n">
-        <v>13</v>
-      </c>
-      <c r="E214" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>21</v>
-      </c>
-      <c r="B215" t="s">
-        <v>16</v>
-      </c>
-      <c r="C215" t="s">
-        <v>60</v>
-      </c>
-      <c r="D215" t="n">
-        <v>13</v>
-      </c>
-      <c r="E215" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>21</v>
-      </c>
-      <c r="B216" t="s">
-        <v>16</v>
-      </c>
-      <c r="C216" t="s">
-        <v>61</v>
-      </c>
-      <c r="D216" t="n">
-        <v>13</v>
-      </c>
-      <c r="E216" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>21</v>
-      </c>
-      <c r="B217" t="s">
-        <v>16</v>
-      </c>
-      <c r="C217" t="s">
-        <v>62</v>
-      </c>
-      <c r="D217" t="n">
-        <v>13</v>
-      </c>
-      <c r="E217" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>21</v>
-      </c>
-      <c r="B218" t="s">
-        <v>16</v>
-      </c>
-      <c r="C218" t="s">
-        <v>63</v>
-      </c>
-      <c r="D218" t="n">
-        <v>13</v>
-      </c>
-      <c r="E218" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>21</v>
-      </c>
-      <c r="B219" t="s">
-        <v>16</v>
-      </c>
-      <c r="C219" t="s">
-        <v>64</v>
-      </c>
-      <c r="D219" t="n">
-        <v>13</v>
-      </c>
-      <c r="E219" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>21</v>
-      </c>
-      <c r="B220" t="s">
-        <v>16</v>
-      </c>
-      <c r="C220" t="s">
-        <v>65</v>
-      </c>
-      <c r="D220" t="n">
-        <v>13</v>
-      </c>
-      <c r="E220" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>21</v>
-      </c>
-      <c r="B221" t="s">
-        <v>16</v>
-      </c>
-      <c r="C221" t="s">
-        <v>66</v>
-      </c>
-      <c r="D221" t="n">
-        <v>13</v>
-      </c>
-      <c r="E221" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>21</v>
-      </c>
-      <c r="B222" t="s">
-        <v>16</v>
-      </c>
-      <c r="C222" t="s">
-        <v>67</v>
-      </c>
-      <c r="D222" t="n">
-        <v>13</v>
-      </c>
-      <c r="E222" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>21</v>
-      </c>
-      <c r="B223" t="s">
-        <v>16</v>
-      </c>
-      <c r="C223" t="s">
-        <v>68</v>
-      </c>
-      <c r="D223" t="n">
-        <v>13</v>
-      </c>
-      <c r="E223" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>21</v>
-      </c>
-      <c r="B224" t="s">
-        <v>16</v>
-      </c>
-      <c r="C224" t="s">
-        <v>69</v>
-      </c>
-      <c r="D224" t="n">
-        <v>13</v>
-      </c>
-      <c r="E224" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>21</v>
-      </c>
-      <c r="B225" t="s">
-        <v>16</v>
-      </c>
-      <c r="C225" t="s">
-        <v>70</v>
-      </c>
-      <c r="D225" t="n">
-        <v>13</v>
-      </c>
-      <c r="E225" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>21</v>
-      </c>
-      <c r="B226" t="s">
-        <v>16</v>
-      </c>
-      <c r="C226" t="s">
-        <v>71</v>
-      </c>
-      <c r="D226" t="n">
-        <v>13</v>
-      </c>
-      <c r="E226" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>21</v>
-      </c>
-      <c r="B227" t="s">
-        <v>16</v>
-      </c>
-      <c r="C227" t="s">
-        <v>72</v>
-      </c>
-      <c r="D227" t="n">
-        <v>13</v>
-      </c>
-      <c r="E227" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>21</v>
-      </c>
-      <c r="B228" t="s">
-        <v>16</v>
-      </c>
-      <c r="C228" t="s">
-        <v>73</v>
-      </c>
-      <c r="D228" t="n">
-        <v>13</v>
-      </c>
-      <c r="E228" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>21</v>
-      </c>
-      <c r="B229" t="s">
-        <v>16</v>
-      </c>
-      <c r="C229" t="s">
-        <v>74</v>
-      </c>
-      <c r="D229" t="n">
-        <v>13</v>
-      </c>
-      <c r="E229" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>21</v>
-      </c>
-      <c r="B230" t="s">
-        <v>16</v>
-      </c>
-      <c r="C230" t="s">
-        <v>75</v>
-      </c>
-      <c r="D230" t="n">
-        <v>13</v>
-      </c>
-      <c r="E230" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>21</v>
-      </c>
-      <c r="B231" t="s">
-        <v>16</v>
-      </c>
-      <c r="C231" t="s">
-        <v>76</v>
-      </c>
-      <c r="D231" t="n">
-        <v>13</v>
-      </c>
-      <c r="E231" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>21</v>
-      </c>
-      <c r="B232" t="s">
-        <v>16</v>
-      </c>
-      <c r="C232" t="s">
-        <v>77</v>
-      </c>
-      <c r="D232" t="n">
-        <v>13</v>
-      </c>
-      <c r="E232" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>21</v>
-      </c>
-      <c r="B233" t="s">
-        <v>16</v>
-      </c>
-      <c r="C233" t="s">
-        <v>78</v>
-      </c>
-      <c r="D233" t="n">
-        <v>13</v>
-      </c>
-      <c r="E233" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>21</v>
-      </c>
-      <c r="B234" t="s">
-        <v>16</v>
-      </c>
-      <c r="C234" t="s">
-        <v>79</v>
-      </c>
-      <c r="D234" t="n">
-        <v>13</v>
-      </c>
-      <c r="E234" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>21</v>
-      </c>
-      <c r="B235" t="s">
-        <v>16</v>
-      </c>
-      <c r="C235" t="s">
-        <v>80</v>
-      </c>
-      <c r="D235" t="n">
-        <v>13</v>
-      </c>
-      <c r="E235" t="n">
         <v>1</v>
       </c>
     </row>
